--- a/output/pdf_financials_xlsx/DE.xlsx
+++ b/output/pdf_financials_xlsx/DE.xlsx
@@ -1069,7 +1069,7 @@
         <v>-0.466214</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.082837</v>
+        <v>0.065163</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>-0.463214</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.508837</v>
+        <v>-0.508837</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>-0.463214</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.508837</v>
+        <v>-0.508837</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>-0.466214</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.082837</v>
+        <v>0.065163</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>0.13131</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.664837</v>
+        <v>0.647163</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>0.739188918752549</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>7.099215385271417</v>
+        <v>2.759639247793271</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>-0.6434813197372881</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>53.0089016167715</v>
+        <v>880.8679772263401</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>-2.607590098324905</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2.169788068739073</v>
+        <v>-2.169788068739073</v>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.185052</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.185052</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>-0.463214</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.508837</v>
+        <v>-0.508837</v>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
@@ -14746,7 +14746,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" s="5" t="n">
         <v>0.185052</v>
       </c>
@@ -26976,7 +26980,7 @@
         <v>-0.463214</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>0.508837</v>
+        <v>-0.508837</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DE.xlsx
+++ b/output/pdf_financials_xlsx/DE.xlsx
@@ -803,7 +803,7 @@
         <v>0.320558</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.973294</v>
+        <v>4.615608</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>8.379431</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3.598081</v>
+        <v>0.955767</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.470777</v>
@@ -888,22 +888,22 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.017946</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004563</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1669,16 +1669,16 @@
         <v>-0.187111</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.302612</v>
+        <v>-0.320558</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0.977615</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.466214</v>
+        <v>-0.470777</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.065163</v>
+        <v>0.052163</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1769,16 +1769,16 @@
         <v>-0.187111</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.302612</v>
+        <v>-0.320558</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.223338</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.13131</v>
+        <v>0.126747</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.647163</v>
+        <v>0.634163</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
         <v>9.19710690693829</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.739188918752549</v>
+        <v>0.7135022304860965</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.759639247793271</v>
+        <v>2.704204511534689</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2021,28 +2021,28 @@
         <v>1.447451</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1.18361</v>
+        <v>1.184</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.815</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.143</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.734</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.257</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.543</v>
       </c>
     </row>
     <row r="35">
@@ -2107,28 +2107,28 @@
         <v>1.447451</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.18361</v>
+        <v>1.184</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.815</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.143</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.734</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.257</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.543</v>
       </c>
     </row>
     <row r="37">
@@ -2623,28 +2623,28 @@
         <v>0.352687</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.30839</v>
+        <v>0.308</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.444</v>
+        <v>0.629</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.234</v>
+        <v>0.799</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.131</v>
+        <v>0.988</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.167</v>
+        <v>2.433</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.449</v>
+        <v>1.399</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.823</v>
+        <v>2.566</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.616</v>
+        <v>3.073</v>
       </c>
     </row>
     <row r="49">
@@ -5943,22 +5943,22 @@
         <v>-9.202</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>-15.064</v>
+        <v>-15.729</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>-0.055</v>
+        <v>-1.083</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-1.227</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-11.635</v>
+        <v>-13.127</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-45.605</v>
+        <v>-47.732</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-8.289999999999999</v>
+        <v>-10.723</v>
       </c>
     </row>
     <row r="125">
@@ -5986,22 +5986,22 @@
         <v>4.661</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>11.468</v>
+        <v>10.803</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>2.052</v>
+        <v>1.024</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>9.936</v>
+        <v>8.709</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>11.931</v>
+        <v>10.439</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>15.271</v>
+        <v>13.144</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>2.775</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="126">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16364,7 +16364,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -25746,7 +25750,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -27802,7 +27806,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">

--- a/output/pdf_financials_xlsx/DE.xlsx
+++ b/output/pdf_financials_xlsx/DE.xlsx
@@ -763,31 +763,31 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.322475</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.418</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.845</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>1.353</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>1.902</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>2.191</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>2.374</v>
       </c>
     </row>
     <row r="10">
@@ -5417,28 +5417,28 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>2.709</v>
       </c>
     </row>
     <row r="113">
@@ -16700,7 +16700,11 @@
           <t>Proceeds on disposal of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -17870,7 +17874,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -23532,7 +23540,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DE.xlsx
+++ b/output/pdf_financials_xlsx/DE.xlsx
@@ -3468,28 +3468,28 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.669</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>2.821</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>3.515</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>4.312</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>7.006</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>5.044</v>
       </c>
     </row>
     <row r="68">
@@ -3603,22 +3603,22 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.851</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>1.128</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>1.279</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>1.693</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>2.385</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>2.622</v>
       </c>
     </row>
     <row r="71">
@@ -3646,22 +3646,22 @@
         <v>1.673</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.097</v>
+        <v>0.948</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>1.128</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>1.279</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.224</v>
+        <v>1.917</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.202</v>
+        <v>2.587</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>2.622</v>
       </c>
     </row>
     <row r="72">
@@ -3818,22 +3818,22 @@
         <v>1.024</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.575</v>
+        <v>0.724</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.289</v>
+        <v>1.161</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2.649</v>
+        <v>1.37</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>4.43</v>
+        <v>2.737</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>3.978</v>
+        <v>1.593</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>6.394</v>
+        <v>3.772</v>
       </c>
     </row>
     <row r="76">
@@ -4039,22 +4039,22 @@
         <v>0.566895844899005</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1.120740910130345</v>
+        <v>1.159661559570089</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.016560165601656</v>
+        <v>1.067320673206732</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.9571930852622327</v>
+        <v>0.994667447992968</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.7837266887153469</v>
+        <v>0.8130421984034909</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1.062759299627312</v>
+        <v>1.104686730890936</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>1.133097804535131</v>
+        <v>1.180359782256029</v>
       </c>
     </row>
     <row r="81">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001228</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.003053</v>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.012438</v>
+        <v>0.01121</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.09307699999999999</v>
@@ -5159,7 +5159,7 @@
         <v>1.178888</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-1.578</v>
@@ -7402,7 +7402,11 @@
           <t>Current portion of lease obligations (note 12)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8910,7 +8914,11 @@
           <t>Current portion of lease obligations (note 14)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -19204,7 +19212,11 @@
           <t>Changes in non-cash operating working capital (note 21)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -20184,7 +20196,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -22756,7 +22772,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E227" s="5" t="n">
         <v>-0.001228</v>
       </c>
